--- a/artfynd/A 59143-2025 artfynd.xlsx
+++ b/artfynd/A 59143-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,10 +821,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127420117</v>
+        <v>136895488</v>
       </c>
       <c r="B3" t="n">
-        <v>106244</v>
+        <v>57186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,53 +832,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NNO Nygård, Vstm</t>
+          <t>Nygård NO, Skultuna sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577122</v>
+        <v>577185</v>
       </c>
       <c r="R3" t="n">
-        <v>6622158</v>
+        <v>6622244</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,17 +898,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På mossa i gles tallskog.</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,31 +922,30 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Åkerberg</t>
+          <t>Anette och Rune Berglinn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Åkerberg, Thommy Åkerberg</t>
+          <t>Anette och Rune Berglinn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127420117</t>
+          <t>https://artportalen.se/Sighting/136895488</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127420135</v>
+        <v>127420117</v>
       </c>
       <c r="B4" t="n">
         <v>106244</v>
@@ -975,15 +975,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -992,10 +996,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577121</v>
+        <v>577122</v>
       </c>
       <c r="R4" t="n">
-        <v>6622139</v>
+        <v>6622158</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1058,6 +1062,126 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420117</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127420135</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NNO Nygård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>577121</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6622139</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På mossa i gles tallskog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg, Thommy Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127420135</t>
         </is>
@@ -1068,6 +1192,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59143-2025 artfynd.xlsx
+++ b/artfynd/A 59143-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,10 +821,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136895488</v>
+        <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57186</v>
+        <v>57195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,34 +832,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -898,22 +898,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,16 +939,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136895488</t>
+          <t>https://artportalen.se/Sighting/137021038</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127420117</v>
+        <v>136895488</v>
       </c>
       <c r="B4" t="n">
-        <v>106244</v>
+        <v>57186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,53 +956,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NNO Nygård, Vstm</t>
+          <t>Nygård NO, Skultuna sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577122</v>
+        <v>577185</v>
       </c>
       <c r="R4" t="n">
-        <v>6622158</v>
+        <v>6622244</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,17 +1022,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På mossa i gles tallskog.</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,31 +1046,30 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Michael Åkerberg</t>
+          <t>Anette och Rune Berglinn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Michael Åkerberg, Thommy Åkerberg</t>
+          <t>Anette och Rune Berglinn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127420117</t>
+          <t>https://artportalen.se/Sighting/136895488</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127420135</v>
+        <v>127420117</v>
       </c>
       <c r="B5" t="n">
         <v>106244</v>
@@ -1099,15 +1099,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1116,10 +1120,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577121</v>
+        <v>577122</v>
       </c>
       <c r="R5" t="n">
-        <v>6622139</v>
+        <v>6622158</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1182,6 +1186,126 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127420117</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127420135</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>NNO Nygård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577121</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6622139</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På mossa i gles tallskog.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Åkerberg, Thommy Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127420135</t>
         </is>
@@ -1193,6 +1317,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59143-2025 artfynd.xlsx
+++ b/artfynd/A 59143-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136895488</v>
       </c>
       <c r="B4" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59143-2025 artfynd.xlsx
+++ b/artfynd/A 59143-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>136895488</v>
       </c>
       <c r="B4" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59143-2025 artfynd.xlsx
+++ b/artfynd/A 59143-2025 artfynd.xlsx
@@ -855,11 +855,7 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -978,11 +974,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 59143-2025 artfynd.xlsx
+++ b/artfynd/A 59143-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>136895488</v>
       </c>
       <c r="B4" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59143-2025 artfynd.xlsx
+++ b/artfynd/A 59143-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>136895488</v>
       </c>
       <c r="B4" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59143-2025 artfynd.xlsx
+++ b/artfynd/A 59143-2025 artfynd.xlsx
@@ -824,7 +824,7 @@
         <v>137021038</v>
       </c>
       <c r="B3" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>136895488</v>
       </c>
       <c r="B4" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
